--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:49</t>
+    <t xml:space="preserve">2026-09-09 22:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:36</t>
+    <t xml:space="preserve">2026-09-12 19:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:53</t>
+    <t xml:space="preserve">2026-09-24 00:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:31</t>
+    <t xml:space="preserve">2026-09-27 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3.19</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.08</v>
+        <v>30.78</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.99</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2.67</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.58</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="7">
@@ -653,7 +653,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.55</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.84</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         <v>2024</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.73</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.39</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="11">
@@ -721,7 +721,7 @@
         <v>2024</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.31</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="12">
@@ -738,7 +738,7 @@
         <v>2024</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.15</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="13">
@@ -755,7 +755,7 @@
         <v>2024</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.03</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="14">
@@ -772,7 +772,7 @@
         <v>2024</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>9.97</v>
       </c>
     </row>
     <row r="15">
@@ -789,7 +789,7 @@
         <v>2024</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.96</v>
+        <v>9.61</v>
       </c>
     </row>
     <row r="16">
@@ -806,7 +806,7 @@
         <v>2024</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.96</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="17">
@@ -823,7 +823,7 @@
         <v>2024</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.9</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="18">
@@ -840,7 +840,7 @@
         <v>2024</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.75</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="19">
@@ -857,7 +857,7 @@
         <v>2024</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.58</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="20">
@@ -874,7 +874,7 @@
         <v>2024</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.58</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="21">
@@ -891,7 +891,7 @@
         <v>2024</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.35</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="22">
@@ -908,7 +908,7 @@
         <v>2024</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.23</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         <v>2024</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.12</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>2024</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.15</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="25">
@@ -959,7 +959,7 @@
         <v>2024</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.2</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="26">
@@ -976,7 +976,7 @@
         <v>2024</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.26</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="27">
@@ -993,7 +993,7 @@
         <v>2024</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.33</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="28">
@@ -1010,7 +1010,7 @@
         <v>2024</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.42</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="29">
@@ -1027,7 +1027,7 @@
         <v>2024</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-1.01</v>
+        <v>-10.11</v>
       </c>
     </row>
     <row r="30">
@@ -1044,7 +1044,7 @@
         <v>2024</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-1.81</v>
+        <v>-18.07</v>
       </c>
     </row>
     <row r="31">
@@ -1061,7 +1061,7 @@
         <v>2024</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-2.39</v>
+        <v>-23.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-10-01 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:59</t>
+    <t xml:space="preserve">2026-10-02 13:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:23</t>
+    <t xml:space="preserve">2026-10-05 08:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
